--- a/EXECUTIVE_TEAM_AUDIT_REPORT_22_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_22_Oct_2026.xlsx
@@ -823,7 +823,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1151,10 +1151,8 @@
           <t>Radhika Singh Bohara</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9851019163</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9851019163</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -1169,10 +1167,8 @@
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9840255166</t>
-        </is>
+      <c r="U2" s="3" t="n">
+        <v>9840255166</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -1189,10 +1185,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.71663</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.71663</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -1244,25 +1238,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>L59-1</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.37006</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.37006</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">
@@ -1363,10 +1353,8 @@
           <t>Radhika Singh Bohara</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9851019163</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9851019163</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1381,10 +1369,8 @@
       </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>9840255166</t>
-        </is>
+      <c r="U3" s="3" t="n">
+        <v>9840255166</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -1401,10 +1387,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>27.71663</t>
-        </is>
+      <c r="Y3" s="3" t="n">
+        <v>27.71663</v>
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
@@ -1456,25 +1440,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>L59-1</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>85.37006</t>
-        </is>
+      <c r="AP3" s="3" t="n">
+        <v>85.37006</v>
       </c>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
@@ -1575,10 +1555,8 @@
           <t>Akkal bhujel</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9863336156</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9863336156</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1593,10 +1571,8 @@
       </c>
       <c r="S4" s="3" t="inlineStr"/>
       <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>9868348711</t>
-        </is>
+      <c r="U4" s="3" t="n">
+        <v>9868348711</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
@@ -1613,10 +1589,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.705759</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.705759</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1668,25 +1642,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>1,9</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.33779</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.33779</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
@@ -1787,10 +1757,8 @@
           <t>Suman Ghimire</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9862428157</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9862428157</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1805,10 +1773,8 @@
       </c>
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>9862428157</t>
-        </is>
+      <c r="U5" s="3" t="n">
+        <v>9862428157</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
@@ -1825,10 +1791,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>27.70804</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>27.70804</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -1866,10 +1830,8 @@
           <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
-      <c r="AH5" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH5" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI5" s="3" t="inlineStr"/>
       <c r="AJ5" s="3" t="inlineStr"/>
@@ -1884,25 +1846,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>L6-3</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.33906</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.33906</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : skycom iptv issue  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_22_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_22_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -544,20 +544,38 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="B4" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -628,7 +646,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -651,7 +669,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -662,19 +680,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -689,12 +707,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -710,6 +729,11 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>Grand Total</t>
         </is>
       </c>
@@ -717,26 +741,32 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -749,7 +779,10 @@
       <c r="B4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -763,7 +796,10 @@
         <v>3</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -777,7 +813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX5"/>
+  <dimension ref="A1:AX7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -800,7 +836,7 @@
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
@@ -814,7 +850,7 @@
     <col width="31" customWidth="1" min="32" max="32"/>
     <col width="30" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="20" customWidth="1" min="38" max="38"/>
@@ -823,7 +859,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1894,6 +1930,422 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 10:57 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1375738</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Seraj Khan</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Seraj Khan</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9706078417</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>21 Oct 2026 01:23:23 PM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>KLK9706078417</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>21 Oct 2026 01:23:23 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 10:57:01 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>Chamati Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>9860991002@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>07:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Sameer Thapa</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>CDB311</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>21h 33m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>21h 33m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 10:56 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1375738</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Seraj Khan</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Seraj Khan</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9706078417</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>21 Oct 2026 01:23:23 PM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>KLK9706078417</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>21 Oct 2026 01:23:23 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 10:57:01 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Chamati Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>9860991002@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>07:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Sameer Thapa</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>CDB311</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>21h 33m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>21h 33m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_22_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_22_Oct_2026.xlsx
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -680,19 +680,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -748,10 +748,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -796,10 +796,10 @@
         <v>3</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -813,7 +813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX7"/>
+  <dimension ref="A1:AX8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1997,10 +1997,8 @@
           <t>Seraj Khan</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9706078417</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9706078417</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -2090,10 +2088,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
@@ -2104,7 +2100,7 @@
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
@@ -2205,10 +2201,8 @@
           <t>Seraj Khan</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9706078417</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9706078417</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -2298,10 +2292,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
@@ -2312,35 +2304,251 @@
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>21h 33m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>21h 33m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS7" s="3" t="inlineStr">
-        <is>
-          <t>21h 33m</t>
-        </is>
-      </c>
-      <c r="AT7" s="3" t="inlineStr">
-        <is>
-          <t>21h 33m</t>
-        </is>
-      </c>
-      <c r="AU7" s="3" t="inlineStr">
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 11:12 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1375958</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Sumana Karki</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Sumana Karki</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9763696933</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 09:29:24 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9865452412</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 09:29:24 AM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 11:12:23 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.70738</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Chhauni,Jansewa marg,opposite to Purna Kaja Ghar,Kathmandu-15, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>sumanaz123@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>01:12 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>CDB383</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.29804</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>1h 42m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>1h 42m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV7" s="3" t="inlineStr">
+      <c r="AV8" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AW7" s="3" t="inlineStr">
+      <c r="AW8" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX7" s="3" t="inlineStr">
+      <c r="AX8" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_22_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_22_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -657,19 +657,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
     </row>
@@ -680,19 +680,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -757,7 +757,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -773,7 +773,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -787,19 +787,35 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" s="4" t="n">
+      <c r="B6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="4" t="n">
-        <v>5</v>
+      <c r="D6" s="4" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -813,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX8"/>
+  <dimension ref="A1:AX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2405,10 +2421,8 @@
           <t>Sumana Karki</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9763696933</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9763696933</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2443,10 +2457,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.70738</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.70738</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2502,47 +2514,43 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>CDB383</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.29804</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.29804</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>1h 42m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>1h 42m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS8" s="3" t="inlineStr">
-        <is>
-          <t>1h 42m</t>
-        </is>
-      </c>
-      <c r="AT8" s="3" t="inlineStr">
-        <is>
-          <t>1h 42m</t>
-        </is>
-      </c>
-      <c r="AU8" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV8" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW8" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -2551,6 +2559,438 @@
       <c r="AX8" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 11:29 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1375658</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Radhika Singh Bohara</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Radhika Singh Bohara</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9851019163</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 11:29:08 AM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9840255166</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>21 Oct 2026 08:44:28 AM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 11:29:08 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>27.71663</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Nayabasti Youth Club Gokarneshwor jorpati, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>radhasub35@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>11:29 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>L59-1</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>85.37006</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 44m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 11:24 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv box issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>iptv box issue</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1375471</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Akshya lalwani</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Akshya lalwani</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9841529717</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 11:24:36 AM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9841529717</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 05:37:12 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 11:24:36 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>27.703513</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Near Global Ime Bank charkhal road kamalpokhar, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>akshayalalwani44@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>13:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Basnet</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>4,16</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>85.32474</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv box issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>1d 17h 47m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv box issue  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_22_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_22_Oct_2026.xlsx
@@ -875,7 +875,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2629,10 +2629,8 @@
           <t>Radhika Singh Bohara</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9851019163</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9851019163</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2667,10 +2665,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>27.71663</t>
-        </is>
+      <c r="Y9" s="3" t="n">
+        <v>27.71663</v>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
@@ -2726,25 +2722,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>L59-1</t>
         </is>
       </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>85.37006</t>
-        </is>
+      <c r="AP9" s="3" t="n">
+        <v>85.37006</v>
       </c>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
@@ -2845,10 +2837,8 @@
           <t>Akshya lalwani</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9841529717</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9841529717</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2883,10 +2873,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>27.703513</t>
-        </is>
+      <c r="Y10" s="3" t="n">
+        <v>27.703513</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -2942,25 +2930,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>4,16</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>85.32474</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>85.32474000000001</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv box issue  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_22_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_22_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -634,19 +634,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>27.3%</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>18.2%</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -745,13 +745,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -829,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX10"/>
+  <dimension ref="A1:AX12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -875,7 +875,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2978,6 +2978,434 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 12:12 PM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>no light blinking</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1375817</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Akkal bhujel</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Akkal bhujel</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9863336156</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 12:12:00 PM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9868348711</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>21 Oct 2026 07:38:29 PM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 12:12:00 PM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>27.705759</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Universal Secondary School - School P8FR+493 Kathmandu , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>subhamhonihh@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr"/>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Pramila Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>1,9</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>85.33779</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>16h 33m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 12:11 PM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1375673</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Sushil Gauli</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Sushil Gauli</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9801042619</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 12:11:16 PM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9813341722</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>21 Oct 2026 09:28:13 AM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 12:11:16 PM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.69904</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Kageshwari Manohara Near By Hanuman Mandir, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>kumargauli@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>12:11 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Sagar Khadka</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>L34-6</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.371</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 43m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_22_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_22_Oct_2026.xlsx
@@ -875,7 +875,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3045,10 +3045,8 @@
           <t>Akkal bhujel</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9863336156</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9863336156</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -3083,10 +3081,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>27.705759</t>
-        </is>
+      <c r="Y11" s="3" t="n">
+        <v>27.705759</v>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
@@ -3138,25 +3134,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>1,9</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>85.33779</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>85.33779</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
@@ -3257,10 +3249,8 @@
           <t>Sushil Gauli</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9801042619</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9801042619</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -3295,10 +3285,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.69904</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.69904</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -3354,25 +3342,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>L34-6</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.371</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.371</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_22_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_22_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>6</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -657,19 +657,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -764,10 +764,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -812,10 +812,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -829,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX12"/>
+  <dimension ref="A1:AX13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -875,7 +875,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3390,6 +3390,218 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 1:25 PM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374322</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Badri Kuamar Rai</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Badri Kuamar Rai</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9862297207</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 10:23:54 AM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9841168136</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>18 Oct 2026 02:51:10 PM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 01:25:45 PM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>27.648692</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>Nakhipot Basket Ball court,Bishal Chowk - Nakhipot Rd, Lalitpur 44700, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>yalung3695@hotmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr"/>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Rawat</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>3,7</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>85.317467</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 1m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>3d 22h 34m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_22_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_22_Oct_2026.xlsx
@@ -875,7 +875,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3457,10 +3457,8 @@
           <t>Badri Kuamar Rai</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9862297207</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9862297207</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3495,10 +3493,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>27.648692</t>
-        </is>
+      <c r="Y13" s="3" t="n">
+        <v>27.648692</v>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
@@ -3550,25 +3546,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>3,7</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>85.317467</t>
-        </is>
+      <c r="AP13" s="3" t="n">
+        <v>85.31746699999999</v>
       </c>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue    has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_22_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_22_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>30.0%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>6</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -634,19 +634,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>35.7%</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -773,7 +773,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Configuration Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -789,7 +789,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -803,19 +803,35 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" s="4" t="n">
+      <c r="B7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="4" t="n">
-        <v>8</v>
+      <c r="D7" s="4" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -829,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX13"/>
+  <dimension ref="A1:AX15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -840,12 +856,12 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -875,7 +891,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3594,6 +3610,414 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 2:04 PM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : inetrt not working  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>inetrt not working</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1375535</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil prasad kushwaha</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil prasad kushwaha</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9841989564</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 02:04:19 PM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>BKT9841989564</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 08:28:52 PM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 02:04:19 PM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr"/>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>near by Lokanthali Madhyapur Thimi 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>9841989564@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr"/>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>CDB454</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr"/>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : inetrt not working  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>1d 17h 35m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : inetrt not working  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 1:49 PM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>inetrt not working</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1375535</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Sunil prasad kushwaha</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Sunil prasad kushwaha</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9841989564</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 02:04:19 PM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>BKT9841989564</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 08:28:52 PM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 02:04:19 PM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>near by Lokanthali Madhyapur Thimi 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>9841989564@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Configuration Issue</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr"/>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>CDB454</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>1d 17h 35m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX15" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_22_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_22_Oct_2026.xlsx
@@ -891,7 +891,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3677,10 +3677,8 @@
           <t>Sunil prasad kushwaha</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9841989564</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9841989564</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3766,10 +3764,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
@@ -3780,7 +3776,7 @@
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : inetrt not working  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
@@ -3881,10 +3877,8 @@
           <t>Sunil prasad kushwaha</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9841989564</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9841989564</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -3970,10 +3964,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
@@ -3984,7 +3976,7 @@
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_22_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_22_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -546,36 +546,54 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>42.9%</t>
+      <c r="B5" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>46.7%</t>
         </is>
       </c>
     </row>
@@ -646,7 +664,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -657,19 +675,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>26.7%</t>
         </is>
       </c>
     </row>
@@ -692,7 +710,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -845,7 +863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX15"/>
+  <dimension ref="A1:AX16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -891,7 +909,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4010,6 +4028,226 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 2:39 PM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : skycom iptv issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>skycom iptv issue</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1374937</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Suman Ghimire</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Suman Ghimire</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9862428157</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 02:39:49 PM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9862428157</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>19 Oct 2026 02:37:02 PM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>22 Oct 2026 02:39:49 PM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>27.70804</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Near HEMS School, Ratopul, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>suman@seedinnovations.com.np</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>06:02 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Salbin Ghale</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>L6-3</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>85.33906</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : skycom iptv issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>3d 2m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : skycom iptv issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX16" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_22_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_22_Oct_2026.xlsx
@@ -909,7 +909,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4095,10 +4095,8 @@
           <t>Suman Ghimire</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9862428157</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9862428157</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -4133,10 +4131,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>27.70804</t>
-        </is>
+      <c r="Y16" s="3" t="n">
+        <v>27.70804</v>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
@@ -4174,10 +4170,8 @@
           <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
-      <c r="AH16" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH16" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI16" s="3" t="inlineStr">
         <is>
@@ -4196,25 +4190,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>L6-3</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>85.33906</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>85.33906</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : skycom iptv issue  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
